--- a/RiggingCalculations_template.xlsx
+++ b/RiggingCalculations_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2 Python\Python\RiggingCalcsTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7FD3CF7-59BA-435B-9555-4A1633CF3B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7414D5B0-90E3-462E-8D6F-D3589E87133E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13605" yWindow="-21600" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{7A3C2ED0-1148-479D-88A7-9F51B0BC8950}"/>
+    <workbookView xWindow="-12195" yWindow="-21600" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{7A3C2ED0-1148-479D-88A7-9F51B0BC8950}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="118">
   <si>
     <t>Weight of object (t)</t>
   </si>
@@ -195,9 +195,6 @@
   </si>
   <si>
     <t>Max. dynamic load on item (kN)</t>
-  </si>
-  <si>
-    <t>SHL * DAF</t>
   </si>
   <si>
     <t>F_leg1</t>
@@ -779,7 +776,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -885,6 +882,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -961,7 +961,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>109910</xdr:colOff>
+      <xdr:colOff>103560</xdr:colOff>
       <xdr:row>56</xdr:row>
       <xdr:rowOff>164492</xdr:rowOff>
     </xdr:to>
@@ -1593,7 +1593,7 @@
   <sheetData>
     <row r="2" spans="2:2" ht="348" x14ac:dyDescent="0.35">
       <c r="B2" s="49" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1615,12 +1615,12 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C3" s="38"/>
       <c r="D3" s="39"/>
@@ -1628,7 +1628,7 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B4" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C4" s="38"/>
       <c r="D4" s="39"/>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C5" s="41"/>
       <c r="D5" s="39"/>
@@ -1644,7 +1644,7 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="38"/>
       <c r="D6" s="39"/>
@@ -1652,7 +1652,7 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" s="38"/>
       <c r="D7" s="39"/>
@@ -1671,7 +1671,7 @@
       <c r="D10" s="39"/>
       <c r="E10" s="40"/>
       <c r="F10" s="33" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.35">
@@ -1680,10 +1680,10 @@
       </c>
       <c r="C12" s="1"/>
       <c r="E12" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" t="s">
         <v>71</v>
-      </c>
-      <c r="F12" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.35">
@@ -1767,7 +1767,7 @@
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>11</v>
@@ -1780,7 +1780,7 @@
         <v>13</v>
       </c>
       <c r="F21" s="45" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
@@ -1788,15 +1788,13 @@
         <v>34</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D22" s="15" t="str">
         <f>IF(D17="","",IF(D20="",D21*D17,D17*D20))</f>
         <v/>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>52</v>
-      </c>
+      <c r="E22" s="2"/>
       <c r="F22" s="45"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.35">
@@ -1811,7 +1809,7 @@
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8"/>
@@ -1823,7 +1821,7 @@
         <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="2"/>
@@ -1834,7 +1832,7 @@
         <v>37</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="2"/>
@@ -1845,7 +1843,7 @@
         <v>38</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="2"/>
@@ -1856,7 +1854,7 @@
         <v>39</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="2"/>
@@ -1876,12 +1874,12 @@
         <v>29</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="2"/>
       <c r="F31" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
@@ -1889,12 +1887,12 @@
         <v>32</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="2"/>
       <c r="F32" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
@@ -1902,12 +1900,12 @@
         <v>30</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="2"/>
       <c r="F33" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
@@ -1915,12 +1913,12 @@
         <v>31</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="2"/>
       <c r="F34" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.35">
@@ -1928,20 +1926,20 @@
         <v>40</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D35" s="5" t="str">
-        <f>IF(D22="","",(D22*D33*D34)/(D31*SIN(RADIANS(D32))))</f>
+        <f>IF(D31="","",(D22*D33*D34)/(D31*SIN(RADIANS(D32))))</f>
         <v/>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="2:6" ht="86" customHeight="1" x14ac:dyDescent="0.35">
@@ -1968,7 +1966,7 @@
   <sheetData>
     <row r="1" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A1" s="34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -1987,7 +1985,7 @@
       </c>
       <c r="C3" s="1"/>
       <c r="BB3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.35">
@@ -2000,7 +1998,7 @@
       </c>
       <c r="D4" s="23"/>
       <c r="BB4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:54" x14ac:dyDescent="0.35">
@@ -2013,18 +2011,18 @@
       </c>
       <c r="D5" s="23"/>
       <c r="BB5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A6" s="31"/>
       <c r="B6" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="23"/>
       <c r="BB6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:54" x14ac:dyDescent="0.35">
@@ -2032,7 +2030,7 @@
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="BB7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:54" x14ac:dyDescent="0.35">
@@ -2043,7 +2041,7 @@
       <c r="C8" s="32"/>
       <c r="D8" s="6"/>
       <c r="BB8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:54" x14ac:dyDescent="0.35">
@@ -2056,7 +2054,7 @@
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="33" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:54" x14ac:dyDescent="0.35">
@@ -2072,19 +2070,19 @@
       <c r="C11" s="32"/>
       <c r="D11" s="6"/>
       <c r="E11" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" t="s">
         <v>71</v>
-      </c>
-      <c r="F11" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A12" s="31"/>
       <c r="B12" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="2"/>
@@ -2117,7 +2115,7 @@
     <row r="15" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A15" s="31"/>
       <c r="B15" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>22</v>
@@ -2125,13 +2123,13 @@
       <c r="D15" s="25"/>
       <c r="E15" s="2"/>
       <c r="F15" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A16" s="31"/>
       <c r="B16" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>23</v>
@@ -2139,7 +2137,7 @@
       <c r="D16" s="25"/>
       <c r="E16" s="2"/>
       <c r="F16" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -2156,7 +2154,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -2173,37 +2171,37 @@
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="31"/>
       <c r="B20" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>41</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="31"/>
       <c r="B21" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>42</v>
       </c>
       <c r="D21" s="19"/>
       <c r="E21" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F21" s="29"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="31"/>
       <c r="B22" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>43</v>
@@ -2213,70 +2211,70 @@
         <v/>
       </c>
       <c r="E22" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F22" s="29"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="31"/>
       <c r="B23" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>44</v>
       </c>
       <c r="D23" s="19"/>
       <c r="E23" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F23" s="29"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="31"/>
       <c r="B24" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F24" s="29"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="31"/>
       <c r="B25" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>46</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F25" s="29"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="31"/>
       <c r="B26" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>47</v>
       </c>
       <c r="D26" s="19"/>
       <c r="E26" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F26" s="29"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="31"/>
       <c r="B27" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>48</v>
@@ -2291,7 +2289,7 @@
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="31"/>
       <c r="B28" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>49</v>
@@ -2316,7 +2314,7 @@
         <v/>
       </c>
       <c r="E29" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F29" s="29"/>
     </row>
@@ -2339,7 +2337,7 @@
         <v>51</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D32" s="26" t="str">
         <f>_xlfn.XLOOKUP(C32,'0-Loads'!C22:C35,'0-Loads'!D22:D35)</f>
@@ -2351,10 +2349,10 @@
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="31"/>
       <c r="B33" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D33" s="27"/>
       <c r="E33" s="2"/>
@@ -2363,10 +2361,10 @@
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="31"/>
       <c r="B34" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D34" s="26" t="str">
         <f>IF(D12="","",(D33*D12)/D29)</f>
@@ -2382,10 +2380,10 @@
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="31"/>
       <c r="B36" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>69</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>70</v>
       </c>
       <c r="D36" s="28" t="str">
         <f>IF(D12="","",D32/D34)</f>
@@ -2402,7 +2400,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B38" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.35">
@@ -2432,7 +2430,7 @@
   <sheetData>
     <row r="1" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A1" s="34" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -2448,7 +2446,7 @@
       </c>
       <c r="C3" s="1"/>
       <c r="BB3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.35">
@@ -2461,7 +2459,7 @@
       </c>
       <c r="D4" s="23"/>
       <c r="BB4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:54" x14ac:dyDescent="0.35">
@@ -2474,18 +2472,18 @@
       </c>
       <c r="D5" s="23"/>
       <c r="BB5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A6" s="31"/>
       <c r="B6" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="23"/>
       <c r="BB6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:54" x14ac:dyDescent="0.35">
@@ -2493,7 +2491,7 @@
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="BB7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:54" x14ac:dyDescent="0.35">
@@ -2504,7 +2502,7 @@
       <c r="C8" s="32"/>
       <c r="D8" s="6"/>
       <c r="BB8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:54" x14ac:dyDescent="0.35">
@@ -2517,7 +2515,7 @@
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="33" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:54" x14ac:dyDescent="0.35">
@@ -2530,18 +2528,18 @@
       <c r="C11" s="32"/>
       <c r="D11" s="6"/>
       <c r="E11" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" t="s">
         <v>71</v>
-      </c>
-      <c r="F11" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:54" x14ac:dyDescent="0.35">
       <c r="B12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>93</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>94</v>
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="2"/>
@@ -2549,10 +2547,10 @@
     </row>
     <row r="13" spans="1:54" x14ac:dyDescent="0.35">
       <c r="B13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>96</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>97</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="2"/>
@@ -2560,12 +2558,15 @@
     </row>
     <row r="14" spans="1:54" x14ac:dyDescent="0.35">
       <c r="B14" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="23"/>
+        <v>66</v>
+      </c>
+      <c r="D14" s="50" t="str">
+        <f>IF(D12="","",9.81*(D12*D13))</f>
+        <v/>
+      </c>
       <c r="E14" s="2"/>
       <c r="F14" s="29"/>
     </row>
@@ -2580,7 +2581,7 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C17" s="13"/>
       <c r="D17" s="48" t="str">
@@ -2592,7 +2593,7 @@
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="35" t="str">
@@ -2604,7 +2605,7 @@
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="36"/>
@@ -2613,7 +2614,7 @@
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B20" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="35" t="str">
@@ -2621,7 +2622,7 @@
         <v/>
       </c>
       <c r="E20" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F20" s="2"/>
     </row>
@@ -2641,7 +2642,7 @@
         <v>51</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D23" s="22" t="str">
         <f>_xlfn.XLOOKUP(C23,'0-Loads'!C22:C35,'0-Loads'!D22:D35)</f>
@@ -2656,10 +2657,10 @@
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>69</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>70</v>
       </c>
       <c r="D25" s="28" t="str">
         <f>IF(D12="","",D23/D20)</f>
@@ -2673,7 +2674,7 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="2:6" ht="80.5" customHeight="1" x14ac:dyDescent="0.35">
